--- a/Carrera-Mapping-Tool.xlsx
+++ b/Carrera-Mapping-Tool.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bmmli.jl/wolke7/Hochschule/25SS/Projekt EPE-CPS/carrera-map/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bmmli.jl/Dokumente/PlatformIO/Projects/Marioehh-Kart_Interface/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3343B617-06D9-384D-95E7-00D353C06451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E54FE2-3DCD-3644-BE09-75A7746EA637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16020" activeTab="1" xr2:uid="{A916984E-B641-6449-9A6C-05EB72DB3162}"/>
   </bookViews>
@@ -720,7 +720,7 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>3</v>
